--- a/public/plantilla-mano-obra.xlsx
+++ b/public/plantilla-mano-obra.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mano de Obra y Subcontratos" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -299,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,47 +330,47 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -407,17 +418,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,7 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -445,13 +456,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,12 +492,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -502,13 +513,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,19 +529,56 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,6 +951,7 @@
     <col width="25.77734375" customWidth="1" style="34" min="8" max="8"/>
     <col width="12.77734375" customWidth="1" style="34" min="9" max="9"/>
     <col width="20.77734375" customWidth="1" style="34" min="10" max="11"/>
+    <col width="13" customWidth="1" style="34" min="11" max="11"/>
     <col width="15" customWidth="1" style="34" min="12" max="12"/>
     <col width="20.77734375" customWidth="1" style="34" min="13" max="13"/>
     <col width="25.77734375" customWidth="1" style="34" min="14" max="14"/>
@@ -1044,10 +1093,10 @@
       </c>
       <c r="B10" s="90" t="n"/>
       <c r="C10" s="84" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="84" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="92" t="n"/>
+      <c r="F10" s="92" t="n"/>
+      <c r="G10" s="93" t="n"/>
       <c r="H10" s="22" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1055,10 +1104,10 @@
       </c>
       <c r="I10" s="90" t="n"/>
       <c r="J10" s="84" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="90" t="n"/>
-      <c r="M10" s="90" t="n"/>
-      <c r="N10" s="84" t="n"/>
+      <c r="K10" s="91" t="n"/>
+      <c r="L10" s="92" t="n"/>
+      <c r="M10" s="92" t="n"/>
+      <c r="N10" s="93" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="34">
       <c r="A11" s="22" t="inlineStr">
@@ -1068,10 +1117,10 @@
       </c>
       <c r="B11" s="90" t="n"/>
       <c r="C11" s="84" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="90" t="n"/>
-      <c r="G11" s="84" t="n"/>
+      <c r="D11" s="91" t="n"/>
+      <c r="E11" s="92" t="n"/>
+      <c r="F11" s="92" t="n"/>
+      <c r="G11" s="93" t="n"/>
       <c r="H11" s="22" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1079,10 +1128,10 @@
       </c>
       <c r="I11" s="90" t="n"/>
       <c r="J11" s="84" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="90" t="n"/>
-      <c r="M11" s="90" t="n"/>
-      <c r="N11" s="84" t="n"/>
+      <c r="K11" s="91" t="n"/>
+      <c r="L11" s="92" t="n"/>
+      <c r="M11" s="92" t="n"/>
+      <c r="N11" s="93" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="34">
       <c r="A12" s="22" t="inlineStr">
@@ -1092,10 +1141,10 @@
       </c>
       <c r="B12" s="90" t="n"/>
       <c r="C12" s="84" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="90" t="n"/>
-      <c r="F12" s="90" t="n"/>
-      <c r="G12" s="84" t="n"/>
+      <c r="D12" s="91" t="n"/>
+      <c r="E12" s="92" t="n"/>
+      <c r="F12" s="92" t="n"/>
+      <c r="G12" s="93" t="n"/>
       <c r="H12" s="22" t="inlineStr">
         <is>
           <t>Responsable del control</t>
@@ -1103,10 +1152,10 @@
       </c>
       <c r="I12" s="90" t="n"/>
       <c r="J12" s="84" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="90" t="n"/>
-      <c r="M12" s="90" t="n"/>
-      <c r="N12" s="84" t="n"/>
+      <c r="K12" s="91" t="n"/>
+      <c r="L12" s="92" t="n"/>
+      <c r="M12" s="92" t="n"/>
+      <c r="N12" s="93" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="40" t="inlineStr">
@@ -1201,27 +1250,27 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="34">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8">
+      <c r="B15" s="91" t="n"/>
+      <c r="C15" s="91" t="n"/>
+      <c r="D15" s="91" t="n"/>
+      <c r="E15" s="91" t="n"/>
+      <c r="F15" s="95" t="n"/>
+      <c r="G15" s="95" t="n"/>
+      <c r="H15" s="96">
         <f>IF(F15="","",F15+N(G15))</f>
         <v/>
       </c>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="8">
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="96">
         <f>IF(OR(H15="",I15=""),"",H15*I15)</f>
         <v/>
       </c>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="8">
+      <c r="K15" s="95" t="n"/>
+      <c r="L15" s="95" t="n"/>
+      <c r="M15" s="96">
         <f>IF(J15="","",J15-N(K15)-N(L15))</f>
         <v/>
       </c>
@@ -1231,27 +1280,27 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="34">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8">
+      <c r="B16" s="91" t="n"/>
+      <c r="C16" s="91" t="n"/>
+      <c r="D16" s="91" t="n"/>
+      <c r="E16" s="91" t="n"/>
+      <c r="F16" s="95" t="n"/>
+      <c r="G16" s="95" t="n"/>
+      <c r="H16" s="96">
         <f>IF(F16="","",F16+N(G16))</f>
         <v/>
       </c>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="8">
+      <c r="I16" s="97" t="n"/>
+      <c r="J16" s="96">
         <f>IF(OR(H16="",I16=""),"",H16*I16)</f>
         <v/>
       </c>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="8">
+      <c r="K16" s="95" t="n"/>
+      <c r="L16" s="95" t="n"/>
+      <c r="M16" s="96">
         <f>IF(J16="","",J16-N(K16)-N(L16))</f>
         <v/>
       </c>
@@ -1261,27 +1310,27 @@
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="34">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8">
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="95" t="n"/>
+      <c r="G17" s="95" t="n"/>
+      <c r="H17" s="96">
         <f>IF(F17="","",F17+N(G17))</f>
         <v/>
       </c>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="8">
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="96">
         <f>IF(OR(H17="",I17=""),"",H17*I17)</f>
         <v/>
       </c>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="8">
+      <c r="K17" s="95" t="n"/>
+      <c r="L17" s="95" t="n"/>
+      <c r="M17" s="96">
         <f>IF(J17="","",J17-N(K17)-N(L17))</f>
         <v/>
       </c>
@@ -1291,27 +1340,27 @@
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="34">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8">
+      <c r="B18" s="91" t="n"/>
+      <c r="C18" s="91" t="n"/>
+      <c r="D18" s="91" t="n"/>
+      <c r="E18" s="91" t="n"/>
+      <c r="F18" s="95" t="n"/>
+      <c r="G18" s="95" t="n"/>
+      <c r="H18" s="96">
         <f>IF(F18="","",F18+N(G18))</f>
         <v/>
       </c>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="8">
+      <c r="I18" s="97" t="n"/>
+      <c r="J18" s="96">
         <f>IF(OR(H18="",I18=""),"",H18*I18)</f>
         <v/>
       </c>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="8">
+      <c r="K18" s="95" t="n"/>
+      <c r="L18" s="95" t="n"/>
+      <c r="M18" s="96">
         <f>IF(J18="","",J18-N(K18)-N(L18))</f>
         <v/>
       </c>
@@ -1321,27 +1370,27 @@
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="34">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8">
+      <c r="B19" s="91" t="n"/>
+      <c r="C19" s="91" t="n"/>
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="91" t="n"/>
+      <c r="F19" s="95" t="n"/>
+      <c r="G19" s="95" t="n"/>
+      <c r="H19" s="96">
         <f>IF(F19="","",F19+N(G19))</f>
         <v/>
       </c>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="8">
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="96">
         <f>IF(OR(H19="",I19=""),"",H19*I19)</f>
         <v/>
       </c>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="8">
+      <c r="K19" s="95" t="n"/>
+      <c r="L19" s="95" t="n"/>
+      <c r="M19" s="96">
         <f>IF(J19="","",J19-N(K19)-N(L19))</f>
         <v/>
       </c>
@@ -1351,27 +1400,27 @@
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="34">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8">
+      <c r="B20" s="91" t="n"/>
+      <c r="C20" s="91" t="n"/>
+      <c r="D20" s="91" t="n"/>
+      <c r="E20" s="91" t="n"/>
+      <c r="F20" s="95" t="n"/>
+      <c r="G20" s="95" t="n"/>
+      <c r="H20" s="96">
         <f>IF(F20="","",F20+N(G20))</f>
         <v/>
       </c>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="8">
+      <c r="I20" s="97" t="n"/>
+      <c r="J20" s="96">
         <f>IF(OR(H20="",I20=""),"",H20*I20)</f>
         <v/>
       </c>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="8">
+      <c r="K20" s="95" t="n"/>
+      <c r="L20" s="95" t="n"/>
+      <c r="M20" s="96">
         <f>IF(J20="","",J20-N(K20)-N(L20))</f>
         <v/>
       </c>
@@ -1381,27 +1430,27 @@
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="34">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8">
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="95" t="n"/>
+      <c r="G21" s="95" t="n"/>
+      <c r="H21" s="96">
         <f>IF(F21="","",F21+N(G21))</f>
         <v/>
       </c>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="8">
+      <c r="I21" s="97" t="n"/>
+      <c r="J21" s="96">
         <f>IF(OR(H21="",I21=""),"",H21*I21)</f>
         <v/>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="8">
+      <c r="K21" s="95" t="n"/>
+      <c r="L21" s="95" t="n"/>
+      <c r="M21" s="96">
         <f>IF(J21="","",J21-N(K21)-N(L21))</f>
         <v/>
       </c>
@@ -1411,27 +1460,27 @@
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="34">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8">
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="95" t="n"/>
+      <c r="G22" s="95" t="n"/>
+      <c r="H22" s="96">
         <f>IF(F22="","",F22+N(G22))</f>
         <v/>
       </c>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="8">
+      <c r="I22" s="97" t="n"/>
+      <c r="J22" s="96">
         <f>IF(OR(H22="",I22=""),"",H22*I22)</f>
         <v/>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="8">
+      <c r="K22" s="95" t="n"/>
+      <c r="L22" s="95" t="n"/>
+      <c r="M22" s="96">
         <f>IF(J22="","",J22-N(K22)-N(L22))</f>
         <v/>
       </c>
@@ -1441,27 +1490,27 @@
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="34">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8">
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="95" t="n"/>
+      <c r="G23" s="95" t="n"/>
+      <c r="H23" s="96">
         <f>IF(F23="","",F23+N(G23))</f>
         <v/>
       </c>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="8">
+      <c r="I23" s="97" t="n"/>
+      <c r="J23" s="96">
         <f>IF(OR(H23="",I23=""),"",H23*I23)</f>
         <v/>
       </c>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="8">
+      <c r="K23" s="95" t="n"/>
+      <c r="L23" s="95" t="n"/>
+      <c r="M23" s="96">
         <f>IF(J23="","",J23-N(K23)-N(L23))</f>
         <v/>
       </c>
@@ -1471,27 +1520,27 @@
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="34">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8">
+      <c r="B24" s="91" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="91" t="n"/>
+      <c r="E24" s="91" t="n"/>
+      <c r="F24" s="95" t="n"/>
+      <c r="G24" s="95" t="n"/>
+      <c r="H24" s="96">
         <f>IF(F24="","",F24+N(G24))</f>
         <v/>
       </c>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="8">
+      <c r="I24" s="97" t="n"/>
+      <c r="J24" s="96">
         <f>IF(OR(H24="",I24=""),"",H24*I24)</f>
         <v/>
       </c>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="8">
+      <c r="K24" s="95" t="n"/>
+      <c r="L24" s="95" t="n"/>
+      <c r="M24" s="96">
         <f>IF(J24="","",J24-N(K24)-N(L24))</f>
         <v/>
       </c>
@@ -1501,27 +1550,27 @@
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="34">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="24" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8">
+      <c r="B25" s="91" t="n"/>
+      <c r="C25" s="91" t="n"/>
+      <c r="D25" s="91" t="n"/>
+      <c r="E25" s="91" t="n"/>
+      <c r="F25" s="95" t="n"/>
+      <c r="G25" s="95" t="n"/>
+      <c r="H25" s="96">
         <f>IF(F25="","",F25+N(G25))</f>
         <v/>
       </c>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="8">
+      <c r="I25" s="97" t="n"/>
+      <c r="J25" s="96">
         <f>IF(OR(H25="",I25=""),"",H25*I25)</f>
         <v/>
       </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="8">
+      <c r="K25" s="95" t="n"/>
+      <c r="L25" s="95" t="n"/>
+      <c r="M25" s="96">
         <f>IF(J25="","",J25-N(K25)-N(L25))</f>
         <v/>
       </c>
@@ -1531,27 +1580,27 @@
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="34">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8">
+      <c r="B26" s="91" t="n"/>
+      <c r="C26" s="91" t="n"/>
+      <c r="D26" s="91" t="n"/>
+      <c r="E26" s="91" t="n"/>
+      <c r="F26" s="95" t="n"/>
+      <c r="G26" s="95" t="n"/>
+      <c r="H26" s="96">
         <f>IF(F26="","",F26+N(G26))</f>
         <v/>
       </c>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="8">
+      <c r="I26" s="97" t="n"/>
+      <c r="J26" s="96">
         <f>IF(OR(H26="",I26=""),"",H26*I26)</f>
         <v/>
       </c>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="8">
+      <c r="K26" s="95" t="n"/>
+      <c r="L26" s="95" t="n"/>
+      <c r="M26" s="96">
         <f>IF(J26="","",J26-N(K26)-N(L26))</f>
         <v/>
       </c>
@@ -1570,35 +1619,35 @@
       <c r="C27" s="90" t="n"/>
       <c r="D27" s="90" t="n"/>
       <c r="E27" s="84" t="n"/>
-      <c r="F27" s="86">
+      <c r="F27" s="98">
         <f>SUM(F15:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="86">
+      <c r="G27" s="98">
         <f>SUM(G15:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="86">
+      <c r="H27" s="98">
         <f>SUM(H15:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="82">
+      <c r="I27" s="99">
         <f>IF(H27=0,"",J27/H27)</f>
         <v/>
       </c>
-      <c r="J27" s="86">
+      <c r="J27" s="98">
         <f>SUM(J15:J26)</f>
         <v/>
       </c>
-      <c r="K27" s="86">
+      <c r="K27" s="98">
         <f>SUM(K15:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="86">
+      <c r="L27" s="98">
         <f>SUM(L15:L26)</f>
         <v/>
       </c>
-      <c r="M27" s="86">
+      <c r="M27" s="98">
         <f>SUM(M15:M26)</f>
         <v/>
       </c>
@@ -1694,220 +1743,220 @@
       <c r="N30" s="84" t="n"/>
     </row>
     <row r="31" ht="22.05" customHeight="1" s="34">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="8">
+      <c r="B31" s="91" t="n"/>
+      <c r="C31" s="91" t="n"/>
+      <c r="D31" s="91" t="n"/>
+      <c r="E31" s="91" t="n"/>
+      <c r="F31" s="100" t="n"/>
+      <c r="G31" s="100" t="n"/>
+      <c r="H31" s="95" t="n"/>
+      <c r="I31" s="97" t="n"/>
+      <c r="J31" s="96">
         <f>IF(OR(F31="",G31="",H31=""),"",F31*G31*H31)</f>
         <v/>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="96">
         <f>IF(J31="","",J31*N(I31))</f>
         <v/>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="96">
         <f>IF(J31="","",J31+K31)</f>
         <v/>
       </c>
-      <c r="M31" s="24" t="n"/>
-      <c r="N31" s="84" t="n"/>
+      <c r="M31" s="91" t="n"/>
+      <c r="N31" s="93" t="n"/>
     </row>
     <row r="32" ht="22.05" customHeight="1" s="34">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="8">
+      <c r="B32" s="91" t="n"/>
+      <c r="C32" s="91" t="n"/>
+      <c r="D32" s="91" t="n"/>
+      <c r="E32" s="91" t="n"/>
+      <c r="F32" s="100" t="n"/>
+      <c r="G32" s="100" t="n"/>
+      <c r="H32" s="95" t="n"/>
+      <c r="I32" s="97" t="n"/>
+      <c r="J32" s="96">
         <f>IF(OR(F32="",G32="",H32=""),"",F32*G32*H32)</f>
         <v/>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="96">
         <f>IF(J32="","",J32*N(I32))</f>
         <v/>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="96">
         <f>IF(J32="","",J32+K32)</f>
         <v/>
       </c>
-      <c r="M32" s="24" t="n"/>
-      <c r="N32" s="84" t="n"/>
+      <c r="M32" s="91" t="n"/>
+      <c r="N32" s="93" t="n"/>
     </row>
     <row r="33" ht="22.05" customHeight="1" s="34">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="24" t="n"/>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="24" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="8">
+      <c r="B33" s="91" t="n"/>
+      <c r="C33" s="91" t="n"/>
+      <c r="D33" s="91" t="n"/>
+      <c r="E33" s="91" t="n"/>
+      <c r="F33" s="100" t="n"/>
+      <c r="G33" s="100" t="n"/>
+      <c r="H33" s="95" t="n"/>
+      <c r="I33" s="97" t="n"/>
+      <c r="J33" s="96">
         <f>IF(OR(F33="",G33="",H33=""),"",F33*G33*H33)</f>
         <v/>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="96">
         <f>IF(J33="","",J33*N(I33))</f>
         <v/>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="96">
         <f>IF(J33="","",J33+K33)</f>
         <v/>
       </c>
-      <c r="M33" s="24" t="n"/>
-      <c r="N33" s="84" t="n"/>
+      <c r="M33" s="91" t="n"/>
+      <c r="N33" s="93" t="n"/>
     </row>
     <row r="34" ht="22.05" customHeight="1" s="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="8">
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="91" t="n"/>
+      <c r="D34" s="91" t="n"/>
+      <c r="E34" s="91" t="n"/>
+      <c r="F34" s="100" t="n"/>
+      <c r="G34" s="100" t="n"/>
+      <c r="H34" s="95" t="n"/>
+      <c r="I34" s="97" t="n"/>
+      <c r="J34" s="96">
         <f>IF(OR(F34="",G34="",H34=""),"",F34*G34*H34)</f>
         <v/>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="96">
         <f>IF(J34="","",J34*N(I34))</f>
         <v/>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="96">
         <f>IF(J34="","",J34+K34)</f>
         <v/>
       </c>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="84" t="n"/>
+      <c r="M34" s="91" t="n"/>
+      <c r="N34" s="93" t="n"/>
     </row>
     <row r="35" ht="22.05" customHeight="1" s="34">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="24" t="n"/>
-      <c r="D35" s="24" t="n"/>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="8">
+      <c r="B35" s="91" t="n"/>
+      <c r="C35" s="91" t="n"/>
+      <c r="D35" s="91" t="n"/>
+      <c r="E35" s="91" t="n"/>
+      <c r="F35" s="100" t="n"/>
+      <c r="G35" s="100" t="n"/>
+      <c r="H35" s="95" t="n"/>
+      <c r="I35" s="97" t="n"/>
+      <c r="J35" s="96">
         <f>IF(OR(F35="",G35="",H35=""),"",F35*G35*H35)</f>
         <v/>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="96">
         <f>IF(J35="","",J35*N(I35))</f>
         <v/>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="96">
         <f>IF(J35="","",J35+K35)</f>
         <v/>
       </c>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="84" t="n"/>
+      <c r="M35" s="91" t="n"/>
+      <c r="N35" s="93" t="n"/>
     </row>
     <row r="36" ht="22.05" customHeight="1" s="34">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="8">
+      <c r="B36" s="91" t="n"/>
+      <c r="C36" s="91" t="n"/>
+      <c r="D36" s="91" t="n"/>
+      <c r="E36" s="91" t="n"/>
+      <c r="F36" s="100" t="n"/>
+      <c r="G36" s="100" t="n"/>
+      <c r="H36" s="95" t="n"/>
+      <c r="I36" s="97" t="n"/>
+      <c r="J36" s="96">
         <f>IF(OR(F36="",G36="",H36=""),"",F36*G36*H36)</f>
         <v/>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="96">
         <f>IF(J36="","",J36*N(I36))</f>
         <v/>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="96">
         <f>IF(J36="","",J36+K36)</f>
         <v/>
       </c>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="84" t="n"/>
+      <c r="M36" s="91" t="n"/>
+      <c r="N36" s="93" t="n"/>
     </row>
     <row r="37" ht="22.05" customHeight="1" s="34">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="8">
+      <c r="B37" s="91" t="n"/>
+      <c r="C37" s="91" t="n"/>
+      <c r="D37" s="91" t="n"/>
+      <c r="E37" s="91" t="n"/>
+      <c r="F37" s="100" t="n"/>
+      <c r="G37" s="100" t="n"/>
+      <c r="H37" s="95" t="n"/>
+      <c r="I37" s="97" t="n"/>
+      <c r="J37" s="96">
         <f>IF(OR(F37="",G37="",H37=""),"",F37*G37*H37)</f>
         <v/>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="96">
         <f>IF(J37="","",J37*N(I37))</f>
         <v/>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="96">
         <f>IF(J37="","",J37+K37)</f>
         <v/>
       </c>
-      <c r="M37" s="24" t="n"/>
-      <c r="N37" s="84" t="n"/>
+      <c r="M37" s="91" t="n"/>
+      <c r="N37" s="93" t="n"/>
     </row>
     <row r="38" ht="22.05" customHeight="1" s="34">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B38" s="24" t="n"/>
-      <c r="C38" s="24" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="8">
+      <c r="B38" s="91" t="n"/>
+      <c r="C38" s="91" t="n"/>
+      <c r="D38" s="91" t="n"/>
+      <c r="E38" s="91" t="n"/>
+      <c r="F38" s="100" t="n"/>
+      <c r="G38" s="100" t="n"/>
+      <c r="H38" s="95" t="n"/>
+      <c r="I38" s="97" t="n"/>
+      <c r="J38" s="96">
         <f>IF(OR(F38="",G38="",H38=""),"",F38*G38*H38)</f>
         <v/>
       </c>
-      <c r="K38" s="8">
+      <c r="K38" s="96">
         <f>IF(J38="","",J38*N(I38))</f>
         <v/>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="96">
         <f>IF(J38="","",J38+K38)</f>
         <v/>
       </c>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="84" t="n"/>
+      <c r="M38" s="91" t="n"/>
+      <c r="N38" s="93" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
@@ -1923,15 +1972,15 @@
       <c r="G39" s="35" t="n"/>
       <c r="H39" s="35" t="n"/>
       <c r="I39" s="35" t="n"/>
-      <c r="J39" s="86">
+      <c r="J39" s="98">
         <f>SUM(J31:J38)</f>
         <v/>
       </c>
-      <c r="K39" s="86">
+      <c r="K39" s="98">
         <f>SUM(K31:K38)</f>
         <v/>
       </c>
-      <c r="L39" s="86">
+      <c r="L39" s="98">
         <f>SUM(L31:L38)</f>
         <v/>
       </c>
@@ -1959,7 +2008,7 @@
       <c r="M41" s="90" t="n"/>
       <c r="N41" s="84" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="34">
+    <row r="42" ht="68" customHeight="1" s="34">
       <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Subcontratos ejecutados</t>
@@ -1968,12 +2017,12 @@
       <c r="B42" s="90" t="n"/>
       <c r="C42" s="90" t="n"/>
       <c r="D42" s="84" t="n"/>
-      <c r="E42" s="41">
+      <c r="E42" s="101">
         <f>J27</f>
         <v/>
       </c>
       <c r="F42" s="84" t="n"/>
-      <c r="H42" s="24" t="inlineStr">
+      <c r="H42" s="94" t="inlineStr">
         <is>
           <t>El saldo por pagar de cada subcontrato es lo ejecutado menos lo pagado y menos la retegarantía retenida.
 La retegarantía es un porcentaje del valor de cada corte que se retiene al subcontratista hasta la liquidación.
@@ -1996,7 +2045,7 @@
       <c r="B43" s="90" t="n"/>
       <c r="C43" s="90" t="n"/>
       <c r="D43" s="84" t="n"/>
-      <c r="E43" s="41">
+      <c r="E43" s="101">
         <f>K27</f>
         <v/>
       </c>
@@ -2013,7 +2062,7 @@
       <c r="B44" s="90" t="n"/>
       <c r="C44" s="90" t="n"/>
       <c r="D44" s="84" t="n"/>
-      <c r="E44" s="41">
+      <c r="E44" s="101">
         <f>L27</f>
         <v/>
       </c>
@@ -2030,7 +2079,7 @@
       <c r="B45" s="90" t="n"/>
       <c r="C45" s="90" t="n"/>
       <c r="D45" s="84" t="n"/>
-      <c r="E45" s="41">
+      <c r="E45" s="101">
         <f>M27</f>
         <v/>
       </c>
@@ -2047,7 +2096,7 @@
       <c r="B46" s="90" t="n"/>
       <c r="C46" s="90" t="n"/>
       <c r="D46" s="84" t="n"/>
-      <c r="E46" s="41">
+      <c r="E46" s="101">
         <f>L39</f>
         <v/>
       </c>
@@ -2064,7 +2113,7 @@
       <c r="B47" s="90" t="n"/>
       <c r="C47" s="90" t="n"/>
       <c r="D47" s="84" t="n"/>
-      <c r="E47" s="86">
+      <c r="E47" s="98">
         <f>J27+L39</f>
         <v/>
       </c>
@@ -2130,10 +2179,10 @@
       </c>
       <c r="B51" s="90" t="n"/>
       <c r="C51" s="84" t="n"/>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="90" t="n"/>
-      <c r="F51" s="90" t="n"/>
-      <c r="G51" s="84" t="n"/>
+      <c r="D51" s="91" t="n"/>
+      <c r="E51" s="92" t="n"/>
+      <c r="F51" s="92" t="n"/>
+      <c r="G51" s="93" t="n"/>
       <c r="H51" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -2141,10 +2190,10 @@
       </c>
       <c r="I51" s="90" t="n"/>
       <c r="J51" s="84" t="n"/>
-      <c r="K51" s="24" t="n"/>
-      <c r="L51" s="90" t="n"/>
-      <c r="M51" s="90" t="n"/>
-      <c r="N51" s="84" t="n"/>
+      <c r="K51" s="100" t="n"/>
+      <c r="L51" s="92" t="n"/>
+      <c r="M51" s="92" t="n"/>
+      <c r="N51" s="93" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="34">
       <c r="A52" s="22" t="inlineStr">
@@ -2154,10 +2203,10 @@
       </c>
       <c r="B52" s="90" t="n"/>
       <c r="C52" s="84" t="n"/>
-      <c r="D52" s="24" t="n"/>
-      <c r="E52" s="90" t="n"/>
-      <c r="F52" s="90" t="n"/>
-      <c r="G52" s="84" t="n"/>
+      <c r="D52" s="91" t="n"/>
+      <c r="E52" s="92" t="n"/>
+      <c r="F52" s="92" t="n"/>
+      <c r="G52" s="93" t="n"/>
       <c r="H52" s="22" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -2165,10 +2214,10 @@
       </c>
       <c r="I52" s="90" t="n"/>
       <c r="J52" s="84" t="n"/>
-      <c r="K52" s="24" t="n"/>
-      <c r="L52" s="90" t="n"/>
-      <c r="M52" s="90" t="n"/>
-      <c r="N52" s="84" t="n"/>
+      <c r="K52" s="100" t="n"/>
+      <c r="L52" s="92" t="n"/>
+      <c r="M52" s="92" t="n"/>
+      <c r="N52" s="93" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="34">
       <c r="A53" s="22" t="inlineStr">
@@ -2178,10 +2227,10 @@
       </c>
       <c r="B53" s="90" t="n"/>
       <c r="C53" s="84" t="n"/>
-      <c r="D53" s="24" t="n"/>
-      <c r="E53" s="90" t="n"/>
-      <c r="F53" s="90" t="n"/>
-      <c r="G53" s="84" t="n"/>
+      <c r="D53" s="91" t="n"/>
+      <c r="E53" s="92" t="n"/>
+      <c r="F53" s="92" t="n"/>
+      <c r="G53" s="93" t="n"/>
       <c r="H53" s="22" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -2189,12 +2238,13 @@
       </c>
       <c r="I53" s="90" t="n"/>
       <c r="J53" s="84" t="n"/>
-      <c r="K53" s="24" t="n"/>
-      <c r="L53" s="90" t="n"/>
-      <c r="M53" s="90" t="n"/>
-      <c r="N53" s="84" t="n"/>
+      <c r="K53" s="100" t="n"/>
+      <c r="L53" s="92" t="n"/>
+      <c r="M53" s="92" t="n"/>
+      <c r="N53" s="93" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="70">
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="A39:E39"/>
